--- a/Dbtransaction.xlsx
+++ b/Dbtransaction.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JTOSO\Documents\Curso\SapTraining\sap-training-modules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1A7E67-DD88-4F1C-A4E9-9D96EF10D9CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3541B8E6-8B5F-4403-9B3E-E752441E2301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{F7FF0447-7988-4902-B26D-C83EF9D09B04}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>ID</t>
   </si>
@@ -45,21 +45,9 @@
     <t>nombre</t>
   </si>
   <si>
-    <t>lt12</t>
-  </si>
-  <si>
     <t>yupdcontimas</t>
   </si>
   <si>
-    <t>me51n</t>
-  </si>
-  <si>
-    <t>migo</t>
-  </si>
-  <si>
-    <t>va01</t>
-  </si>
-  <si>
     <t>uso</t>
   </si>
   <si>
@@ -96,13 +84,43 @@
     <t>Transacción estandar utilizada para generar manualmente una salida de materiales, descontando del stock los insumos involucrados.</t>
   </si>
   <si>
-    <t>me21n</t>
-  </si>
-  <si>
     <t>Generar pedidos de traslado de materiales sap</t>
   </si>
   <si>
     <t>Transacción utiizada para solicitar insumos, normalmente, desde el warehouse central en Bs. As. Hacia el resto de las sucursales.</t>
+  </si>
+  <si>
+    <t>LT12</t>
+  </si>
+  <si>
+    <t>Me21n</t>
+  </si>
+  <si>
+    <t>Migo</t>
+  </si>
+  <si>
+    <t>Va01</t>
+  </si>
+  <si>
+    <t>Ysd_Imposicion</t>
+  </si>
+  <si>
+    <t>Imposición de ECO's o piezas generadas por interfaz; es decir, todo aquello que tiene datos precargados como destinatarios, destino, etc</t>
+  </si>
+  <si>
+    <t>Imposicion de equipos precargados</t>
+  </si>
+  <si>
+    <t>Me51n</t>
+  </si>
+  <si>
+    <t>Ylt12</t>
+  </si>
+  <si>
+    <t>Confirmacion masiva de OT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transacción utilizada para confirmar de manera masiva todas las Ordenes de trabajo pendientes de confirmación (no todos los procesos permiten confirmacion masiva) </t>
   </si>
 </sst>
 </file>
@@ -515,7 +533,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.36328125" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="41.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="60.36328125" customWidth="1"/>
   </cols>
@@ -528,10 +546,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
@@ -539,13 +557,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
@@ -553,24 +571,24 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>16</v>
@@ -581,13 +599,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
@@ -595,13 +613,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
@@ -609,30 +627,42 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+      <c r="B9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="10" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
@@ -1282,6 +1312,9 @@
       <c r="D90" s="2"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D77">
+    <sortCondition ref="B2:B77"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1300,7 +1333,7 @@
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="str">
         <f>CONCATENATE("        nombre: '",Detalles!B2,"',")</f>
-        <v xml:space="preserve">        nombre: 'lt12',</v>
+        <v xml:space="preserve">        nombre: 'LT12',</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
@@ -1324,19 +1357,19 @@
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
         <f>CONCATENATE("        nombre: '",Detalles!B3,"',")</f>
-        <v xml:space="preserve">        nombre: 'yupdcontimas',</v>
+        <v xml:space="preserve">        nombre: 'Me51n',</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
         <f>CONCATENATE("        uso: '",Detalles!C3,"',")</f>
-        <v xml:space="preserve">        uso: 'Modificación de datos web a nivel contingentación',</v>
+        <v xml:space="preserve">        uso: 'Generación de solped',</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
         <f>CONCATENATE("        explicacion: '",Detalles!D3,"'}")</f>
-        <v xml:space="preserve">        explicacion: 'Transacción utilizada para modificar los totales que se encuentran registrados en la tabla de contingentacion, y son visualizados por via web asociados por programas'}</v>
+        <v xml:space="preserve">        explicacion: 'Transacción utilizada en el proceso de generación de solicitudes para ordenes de compra, debe tener en cuenta que tiene que tener autorizado el GCp correspondiente (Grupo de compra)'}</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
@@ -1348,19 +1381,19 @@
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f>CONCATENATE("        nombre: '",Detalles!B4,"',")</f>
-        <v xml:space="preserve">        nombre: 'me51n',</v>
+        <v xml:space="preserve">        nombre: 'Me21n',</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
         <f>CONCATENATE("        uso: '",Detalles!C4,"',")</f>
-        <v xml:space="preserve">        uso: 'Generación de solped',</v>
+        <v xml:space="preserve">        uso: 'Generar pedidos de traslado de materiales sap',</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
         <f>CONCATENATE("        explicacion: '",Detalles!D4,"'}")</f>
-        <v xml:space="preserve">        explicacion: 'Transacción utilizada en el proceso de generación de solicitudes para ordenes de compra, debe tener en cuenta que tiene que tener autorizado el GCp correspondiente (Grupo de compra)'}</v>
+        <v xml:space="preserve">        explicacion: 'Transacción utiizada para solicitar insumos, normalmente, desde el warehouse central en Bs. As. Hacia el resto de las sucursales.'}</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
@@ -1372,7 +1405,7 @@
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="str">
         <f>CONCATENATE("        nombre: '",Detalles!B5,"',")</f>
-        <v xml:space="preserve">        nombre: 'migo',</v>
+        <v xml:space="preserve">        nombre: 'Migo',</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
@@ -1396,7 +1429,7 @@
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f>CONCATENATE("        nombre: '",Detalles!B6,"',")</f>
-        <v xml:space="preserve">        nombre: 'va01',</v>
+        <v xml:space="preserve">        nombre: 'Va01',</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
@@ -1420,19 +1453,19 @@
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="str">
         <f>CONCATENATE("        nombre: '",Detalles!B7,"',")</f>
-        <v xml:space="preserve">        nombre: 'me21n',</v>
+        <v xml:space="preserve">        nombre: 'Ysd_Imposicion',</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" t="str">
         <f>CONCATENATE("        uso: '",Detalles!C7,"',")</f>
-        <v xml:space="preserve">        uso: 'Generar pedidos de traslado de materiales sap',</v>
+        <v xml:space="preserve">        uso: 'Imposicion de equipos precargados',</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" t="str">
         <f>CONCATENATE("        explicacion: '",Detalles!D7,"'}")</f>
-        <v xml:space="preserve">        explicacion: 'Transacción utiizada para solicitar insumos, normalmente, desde el warehouse central en Bs. As. Hacia el resto de las sucursales.'}</v>
+        <v xml:space="preserve">        explicacion: 'Imposición de ECO's o piezas generadas por interfaz; es decir, todo aquello que tiene datos precargados como destinatarios, destino, etc'}</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
@@ -1444,19 +1477,19 @@
     <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" t="str">
         <f>CONCATENATE("        nombre: '",Detalles!B8,"',")</f>
-        <v xml:space="preserve">        nombre: '',</v>
+        <v xml:space="preserve">        nombre: 'yupdcontimas',</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" t="str">
         <f>CONCATENATE("        uso: '",Detalles!C8,"',")</f>
-        <v xml:space="preserve">        uso: '',</v>
+        <v xml:space="preserve">        uso: 'Modificación de datos web a nivel contingentación',</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" t="str">
         <f>CONCATENATE("        explicacion: '",Detalles!D8,"'}")</f>
-        <v xml:space="preserve">        explicacion: ''}</v>
+        <v xml:space="preserve">        explicacion: 'Transacción utilizada para modificar los totales que se encuentran registrados en la tabla de contingentacion, y son visualizados por via web asociados por programas'}</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.35">
@@ -1468,19 +1501,19 @@
     <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" t="str">
         <f>CONCATENATE("        nombre: '",Detalles!B9,"',")</f>
-        <v xml:space="preserve">        nombre: '',</v>
+        <v xml:space="preserve">        nombre: 'Ylt12',</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" t="str">
         <f>CONCATENATE("        uso: '",Detalles!C9,"',")</f>
-        <v xml:space="preserve">        uso: '',</v>
+        <v xml:space="preserve">        uso: 'Confirmacion masiva de OT',</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" t="str">
         <f>CONCATENATE("        explicacion: '",Detalles!D9,"'}")</f>
-        <v xml:space="preserve">        explicacion: ''}</v>
+        <v xml:space="preserve">        explicacion: 'Transacción utilizada para confirmar de manera masiva todas las Ordenes de trabajo pendientes de confirmación (no todos los procesos permiten confirmacion masiva) '}</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
@@ -1701,5 +1734,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Dbtransaction.xlsx
+++ b/Dbtransaction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JTOSO\Documents\Curso\SapTraining\sap-training-modules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3541B8E6-8B5F-4403-9B3E-E752441E2301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F205034D-94D4-4CEE-A65D-50CF7C7EDDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{F7FF0447-7988-4902-B26D-C83EF9D09B04}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>ID</t>
   </si>
@@ -121,6 +121,15 @@
   </si>
   <si>
     <t xml:space="preserve">Transacción utilizada para confirmar de manera masiva todas las Ordenes de trabajo pendientes de confirmación (no todos los procesos permiten confirmacion masiva) </t>
+  </si>
+  <si>
+    <t>Zv11</t>
+  </si>
+  <si>
+    <t>Creación de HU</t>
+  </si>
+  <si>
+    <t>Transacción utilizada para crear unidades de manipulación (HU) que son contenedores que agrupan piezas por destinos, estos contenedores pueden ser fisicos o solo lógicos.</t>
   </si>
 </sst>
 </file>
@@ -664,13 +673,19 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+      <c r="B10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
@@ -1525,19 +1540,19 @@
     <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" t="str">
         <f>CONCATENATE("        nombre: '",Detalles!B10,"',")</f>
-        <v xml:space="preserve">        nombre: '',</v>
+        <v xml:space="preserve">        nombre: 'Zv11',</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" t="str">
         <f>CONCATENATE("        uso: '",Detalles!C10,"',")</f>
-        <v xml:space="preserve">        uso: '',</v>
+        <v xml:space="preserve">        uso: 'Creación de HU',</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" t="str">
         <f>CONCATENATE("        explicacion: '",Detalles!D10,"'}")</f>
-        <v xml:space="preserve">        explicacion: ''}</v>
+        <v xml:space="preserve">        explicacion: 'Transacción utilizada para crear unidades de manipulación (HU) que son contenedores que agrupan piezas por destinos, estos contenedores pueden ser fisicos o solo lógicos.'}</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.35">

--- a/Dbtransaction.xlsx
+++ b/Dbtransaction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JTOSO\Documents\Curso\SapTraining\sap-training-modules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F205034D-94D4-4CEE-A65D-50CF7C7EDDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC7D8518-4E74-4A6D-A9FD-E9752E1D7C5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{F7FF0447-7988-4902-B26D-C83EF9D09B04}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>ID</t>
   </si>
@@ -130,6 +130,15 @@
   </si>
   <si>
     <t>Transacción utilizada para crear unidades de manipulación (HU) que son contenedores que agrupan piezas por destinos, estos contenedores pueden ser fisicos o solo lógicos.</t>
+  </si>
+  <si>
+    <t>Vl74</t>
+  </si>
+  <si>
+    <t>Impresión de HUs</t>
+  </si>
+  <si>
+    <t>Transacción utilizada para Imprimir los detalles de las unidades de manipulación</t>
   </si>
 </sst>
 </file>
@@ -687,13 +696,19 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="B11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -1564,19 +1579,19 @@
     <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" t="str">
         <f>CONCATENATE("        nombre: '",Detalles!B11,"',")</f>
-        <v xml:space="preserve">        nombre: '',</v>
+        <v xml:space="preserve">        nombre: 'Vl74',</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" t="str">
         <f>CONCATENATE("        uso: '",Detalles!C11,"',")</f>
-        <v xml:space="preserve">        uso: '',</v>
+        <v xml:space="preserve">        uso: 'Impresión de HUs',</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" t="str">
         <f>CONCATENATE("        explicacion: '",Detalles!D11,"'}")</f>
-        <v xml:space="preserve">        explicacion: ''}</v>
+        <v xml:space="preserve">        explicacion: 'Transacción utilizada para Imprimir los detalles de las unidades de manipulación'}</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.35">

--- a/Dbtransaction.xlsx
+++ b/Dbtransaction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JTOSO\Documents\Curso\SapTraining\sap-training-modules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC7D8518-4E74-4A6D-A9FD-E9752E1D7C5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B6BBC7-DDD0-4ACC-813B-74DB8B3D4187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{F7FF0447-7988-4902-B26D-C83EF9D09B04}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>ID</t>
   </si>
@@ -139,6 +139,15 @@
   </si>
   <si>
     <t>Transacción utilizada para Imprimir los detalles de las unidades de manipulación</t>
+  </si>
+  <si>
+    <t>Zrpt0032</t>
+  </si>
+  <si>
+    <t>Consulta de Poblaciones</t>
+  </si>
+  <si>
+    <t>Reporte para conocer el Código postal de una localidad y cuál es la sucursal y centro que lo atiende</t>
   </si>
 </sst>
 </file>
@@ -711,13 +720,19 @@
       </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>11</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="B12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>36</v>
+      </c>
       <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -1603,19 +1618,19 @@
     <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" t="str">
         <f>CONCATENATE("        nombre: '",Detalles!B12,"',")</f>
-        <v xml:space="preserve">        nombre: '',</v>
+        <v xml:space="preserve">        nombre: 'Zrpt0032',</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" t="str">
         <f>CONCATENATE("        uso: '",Detalles!C12,"',")</f>
-        <v xml:space="preserve">        uso: '',</v>
+        <v xml:space="preserve">        uso: 'Consulta de Poblaciones',</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" t="str">
         <f>CONCATENATE("        explicacion: '",Detalles!D12,"'}")</f>
-        <v xml:space="preserve">        explicacion: ''}</v>
+        <v xml:space="preserve">        explicacion: 'Reporte para conocer el Código postal de una localidad y cuál es la sucursal y centro que lo atiende'}</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.35">
